--- a/data/Data_for_figures_4results/Result3_percentage and correlation.xlsx
+++ b/data/Data_for_figures_4results/Result3_percentage and correlation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\State_SDG\Github\SDG_Interactions-driven-by-Urban_Typologies\data\Data_for_figures_4results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\City SDG paper\data for governance capacity\WGI_data_072026\1_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A06962-2011-489C-9C39-839ACD611A72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880757EB-146E-4E55-936D-DC87F6BB6560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="15648" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1308" yWindow="732" windowWidth="19860" windowHeight="9024" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -402,10 +402,10 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>37.104377104377107</v>
+        <v>36.632996632996637</v>
       </c>
       <c r="D2">
-        <v>0.38275087210940079</v>
+        <v>0.3835625094855904</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -416,10 +416,10 @@
         <v>3</v>
       </c>
       <c r="C3">
-        <v>18.98989898989899</v>
+        <v>18.787878787878789</v>
       </c>
       <c r="D3">
-        <v>0.38407890015995222</v>
+        <v>0.38427989373469168</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -430,10 +430,10 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>10.37037037037037</v>
+        <v>10.437710437710439</v>
       </c>
       <c r="D4">
-        <v>0.61203491504489393</v>
+        <v>0.6121222022377214</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -444,10 +444,10 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>13.87205387205387</v>
+        <v>14.27609427609428</v>
       </c>
       <c r="D5">
-        <v>0.46185495742034383</v>
+        <v>0.46089895244931411</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -458,10 +458,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>7.8114478114478114</v>
+        <v>8.2828282828282838</v>
       </c>
       <c r="D6">
-        <v>-0.31600723294516919</v>
+        <v>-0.31621597068096169</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -472,10 +472,10 @@
         <v>3</v>
       </c>
       <c r="C7">
-        <v>4.9831649831649827</v>
+        <v>5.1851851851851851</v>
       </c>
       <c r="D7">
-        <v>-0.3628885698425332</v>
+        <v>-0.36298589170746731</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -486,10 +486,10 @@
         <v>4</v>
       </c>
       <c r="C8">
-        <v>3.8383838383838378</v>
+        <v>3.7710437710437712</v>
       </c>
       <c r="D8">
-        <v>-0.5975384248713389</v>
+        <v>-0.59703796049523494</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -500,10 +500,10 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>5.2525252525252526</v>
+        <v>4.8484848484848486</v>
       </c>
       <c r="D9">
-        <v>-0.45482869393877312</v>
+        <v>-0.45705807550778499</v>
       </c>
     </row>
   </sheetData>
